--- a/Result/profitability/3485.xlsx
+++ b/Result/profitability/3485.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM41"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9325</v>
+        <v>1.9725</v>
       </c>
       <c r="N2" t="n">
-        <v>52.4575</v>
+        <v>52.01625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.89125</v>
+        <v>1.69</v>
       </c>
       <c r="N3" t="n">
-        <v>51.82875</v>
+        <v>51.8275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.51125</v>
+        <v>1.365</v>
       </c>
       <c r="N4" t="n">
-        <v>46.69375</v>
+        <v>45.0925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>1.23625</v>
+        <v>1.41125</v>
       </c>
       <c r="N5" t="n">
-        <v>43.83749999999999</v>
+        <v>43.3075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>4.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.78875</v>
+        <v>1.70875</v>
       </c>
       <c r="N6" t="n">
-        <v>41.9925</v>
+        <v>41.8325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>6.76</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3975</v>
+        <v>2.33625</v>
       </c>
       <c r="N7" t="n">
-        <v>41.595</v>
+        <v>41.68875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -5635,6 +5635,133 @@
       </c>
       <c r="AM41" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>162</v>
+      </c>
+      <c r="D42" t="n">
+        <v>79</v>
+      </c>
+      <c r="E42" t="n">
+        <v>83</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>50</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>30.64%</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>58</v>
+      </c>
+      <c r="K42" t="n">
+        <v>46</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.57875</v>
+      </c>
+      <c r="N42" t="n">
+        <v>54.09125</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-0.4399999999999999</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-0.2603550295857988</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-2.009999999999998</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-0.03777485435068595</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-9.333333333333334</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-4.239999999999995</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.07647907647907637</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
